--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488009_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488009_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7491</v>
+        <v>7.1785</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6527</v>
+        <v>5.9418</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0963</v>
+        <v>1.2367</v>
       </c>
       <c r="G2" t="n">
         <v>5.0387</v>
@@ -610,13 +610,13 @@
         <v>2.5769</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.479</v>
+        <v>-0.0496</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3709</v>
+        <v>0.66</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8499</v>
+        <v>-0.7096</v>
       </c>
       <c r="V2" t="n">
         <v>0.6036</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1647</v>
+        <v>4.6333</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1408</v>
+        <v>5.3675</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0239</v>
+        <v>-0.7342</v>
       </c>
       <c r="G3" t="n">
         <v>-1.0902</v>
@@ -688,13 +688,13 @@
         <v>2.3787</v>
       </c>
       <c r="S3" t="n">
-        <v>1.462</v>
+        <v>0.9305</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4957</v>
+        <v>0.7224</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9663</v>
+        <v>0.2081</v>
       </c>
       <c r="V3" t="n">
         <v>2.4142</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4987</v>
+        <v>4.138</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0587</v>
+        <v>2.6699</v>
       </c>
       <c r="F4" t="n">
-        <v>1.44</v>
+        <v>1.4681</v>
       </c>
       <c r="G4" t="n">
         <v>2.6307</v>
@@ -766,13 +766,13 @@
         <v>1.5858</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4512</v>
+        <v>0.1881</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5505</v>
+        <v>0.0607</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0994</v>
+        <v>0.1275</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2666</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9878</v>
+        <v>3.8756</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8158</v>
+        <v>2.5913</v>
       </c>
       <c r="F5" t="n">
-        <v>1.172</v>
+        <v>1.2843</v>
       </c>
       <c r="G5" t="n">
         <v>0.0428</v>
@@ -844,13 +844,13 @@
         <v>1.9822</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1145</v>
+        <v>-0.2267</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6864</v>
+        <v>0.0891</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4281</v>
+        <v>-0.3158</v>
       </c>
       <c r="V5" t="n">
         <v>2.0772</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. JIMENEZ EXPOSITO</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8269</v>
+        <v>1.6015</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4946</v>
+        <v>2.7421</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3323</v>
+        <v>-1.1406</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2069</v>
+        <v>1.8294</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1909</v>
+        <v>2.1949</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3979</v>
+        <v>-0.3655</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1274</v>
+        <v>3.7523</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0069</v>
+        <v>3.5916</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1205</v>
+        <v>0.1607</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0795</v>
+        <v>-1.9229</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1979</v>
+        <v>-1.3967</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2774</v>
+        <v>-0.5262</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7929</v>
+        <v>1.3876</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7929</v>
+        <v>2.3787</v>
       </c>
       <c r="S7" t="n">
-        <v>0.49</v>
+        <v>-0.4083</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3671</v>
+        <v>-0.0191</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1229</v>
+        <v>-0.3892</v>
       </c>
       <c r="V7" t="n">
-        <v>0.337</v>
+        <v>-1.2071</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.337</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. TRUNO SOMS</t>
+          <t>D. JIMENEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5096</v>
+        <v>1.5846</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8307</v>
+        <v>0.3927</v>
       </c>
       <c r="F8" t="n">
-        <v>0.679</v>
+        <v>1.1919</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7983</v>
+        <v>0.2069</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0556</v>
+        <v>-0.1909</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8539</v>
+        <v>0.3979</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.1274</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0449</v>
+        <v>0.0069</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.1975</v>
+        <v>0.1205</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6456</v>
+        <v>0.0795</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9893</v>
+        <v>-0.1979</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6563</v>
+        <v>0.2774</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3876</v>
+        <v>0.7929</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3787</v>
+        <v>0.7929</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0202</v>
+        <v>0.2478</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3709</v>
+        <v>0.2653</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3911</v>
+        <v>-0.0175</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9405</v>
+        <v>0.337</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0.337</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>P. TRUNO SOMS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2625</v>
+        <v>1.3527</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5154</v>
+        <v>0.8141</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2529</v>
+        <v>0.5386</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8294</v>
+        <v>-0.7983</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1949</v>
+        <v>1.0556</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3655</v>
+        <v>-1.8539</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7523</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5916</v>
+        <v>2.0449</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1607</v>
+        <v>-1.1975</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9229</v>
+        <v>-1.6456</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3967</v>
+        <v>-0.9893</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5262</v>
+        <v>-0.6563</v>
       </c>
       <c r="P9" t="n">
         <v>1.3876</v>
@@ -1156,22 +1156,22 @@
         <v>2.3787</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7473</v>
+        <v>-0.1771</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2458</v>
+        <v>0.3544</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5014999999999999</v>
+        <v>-0.5315</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2071</v>
+        <v>0.9405</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2071</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.093</v>
+        <v>0.5151</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2266</v>
+        <v>1.5365</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1337</v>
+        <v>-1.0214</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2732</v>
@@ -1234,13 +1234,13 @@
         <v>2.3787</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7981</v>
+        <v>0.2203</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0611</v>
+        <v>0.3709</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.263</v>
+        <v>-0.1506</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8107</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0415</v>
+        <v>-1.3191</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1872</v>
+        <v>-0.4928</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.8263</v>
       </c>
       <c r="G12" t="n">
         <v>-1.011</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.2955</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4919</v>
+        <v>0.1863</v>
       </c>
       <c r="U12" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.1092</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6036</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.0209</v>
+        <v>-1.7121</v>
       </c>
       <c r="E13" t="n">
         <v>-1.2765</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7444</v>
+        <v>-0.4356</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5435</v>
@@ -1468,13 +1468,13 @@
         <v>1.5858</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.407</v>
+        <v>-0.0982</v>
       </c>
       <c r="T13" t="n">
         <v>0.1396</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5466</v>
+        <v>-0.2378</v>
       </c>
       <c r="V13" t="n">
         <v>-0.674</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.3062</v>
+        <v>-3.1886</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.8087</v>
+        <v>-1.8876</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4975</v>
+        <v>-1.301</v>
       </c>
       <c r="G14" t="n">
         <v>-3.4308</v>
@@ -1546,13 +1546,13 @@
         <v>1.784</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6177</v>
+        <v>-0.5001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0038</v>
+        <v>-0.0752</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6215000000000001</v>
+        <v>-0.425</v>
       </c>
       <c r="V14" t="n">
         <v>0.9405</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>20.7424</v>
+        <v>21.6782</v>
       </c>
       <c r="E15" t="n">
-        <v>20.4816</v>
+        <v>21.41770000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2607000000000006</v>
+        <v>0.2604999999999995</v>
       </c>
       <c r="G15" t="n">
         <v>5.620200000000002</v>
@@ -1624,13 +1624,13 @@
         <v>19.8224</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5137</v>
+        <v>0.4222000000000002</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8183</v>
+        <v>2.7544</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.332</v>
+        <v>-2.3322</v>
       </c>
       <c r="V15" t="n">
         <v>2.751000000000001</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9476</v>
+        <v>2.1455</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1754</v>
+        <v>4.0736</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2278</v>
+        <v>-1.9281</v>
       </c>
       <c r="G16" t="n">
         <v>2.7442</v>
@@ -1702,13 +1702,13 @@
         <v>1.1893</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0033</v>
+        <v>0.1945</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2351</v>
+        <v>0.1332</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2385</v>
+        <v>0.0613</v>
       </c>
       <c r="V16" t="n">
         <v>0.9908</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ESPINAL REYNOSO</t>
+          <t>J. MORALES MUÑOZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6249</v>
+        <v>0.9053</v>
       </c>
       <c r="E17" t="n">
-        <v>5.7905</v>
+        <v>0.9053</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.1657</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.8364</v>
+        <v>0.9053</v>
       </c>
       <c r="H17" t="n">
-        <v>-4.1422</v>
+        <v>0.3027</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3059</v>
+        <v>0.6027</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.6161</v>
+        <v>0.9053</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.4197</v>
+        <v>0.3027</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8036</v>
+        <v>0.6027</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2203</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7226</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4977</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9896</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.4436</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4539</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>2.2734</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>4.9542</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.6808</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MORALES MUÑOZ</t>
+          <t>R. ALMAGRO LAZARO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9053</v>
+        <v>0.6082</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9053</v>
+        <v>-0.002</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.6103</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9053</v>
+        <v>0.4678</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3027</v>
+        <v>0.0202</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6027</v>
+        <v>0.4477</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9053</v>
+        <v>0.0604</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3027</v>
+        <v>0.0202</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6027</v>
+        <v>0.0402</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.4075</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.4075</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.0578</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.0624</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.0046</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. ALMAGRO LAZARO</t>
+          <t>J. PEREZ CABELLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.524</v>
+        <v>-0.3139</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.002</v>
+        <v>0.2061</v>
       </c>
       <c r="F19" t="n">
-        <v>0.526</v>
+        <v>-0.52</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4678</v>
+        <v>-0.7595</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0202</v>
+        <v>-0.4267</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4477</v>
+        <v>-0.3328</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0604</v>
+        <v>-0.6508</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0202</v>
+        <v>0.1009</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0402</v>
+        <v>-0.7517</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4075</v>
+        <v>-0.1087</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.5276</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4075</v>
+        <v>0.4189</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1982</v>
+        <v>0.3964</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1982</v>
+        <v>0.3964</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1421</v>
+        <v>-0.167</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0624</v>
+        <v>0.2534</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.4204</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2163</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.3873</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MARTINEZ GUZMAN</t>
+          <t>J. ESPINAL REYNOSO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.966</v>
+        <v>-0.3341</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08</v>
+        <v>3.4475</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.046</v>
+        <v>-3.7817</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4002</v>
+        <v>-3.8364</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6349</v>
+        <v>-4.1422</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.035</v>
+        <v>0.3059</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3296</v>
+        <v>-1.6161</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9685</v>
+        <v>-2.4197</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.639</v>
+        <v>0.8036</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7298</v>
+        <v>-2.2203</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3337</v>
+        <v>-1.7226</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3961</v>
+        <v>-0.4977</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0921</v>
+        <v>1.0306</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2496</v>
+        <v>1.1006</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1574</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8701</v>
+        <v>2.2734</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>4.9542</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8701</v>
+        <v>-2.6808</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. PEREZ CABELLO</t>
+          <t>J. MARTINEZ GUZMAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3208</v>
+        <v>-0.6885</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6088</v>
+        <v>0.3856</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.712</v>
+        <v>-1.0741</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7595</v>
+        <v>-0.4002</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4267</v>
+        <v>0.6349</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3328</v>
+        <v>-1.035</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6508</v>
+        <v>0.3296</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1009</v>
+        <v>0.9685</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7517</v>
+        <v>-0.639</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1087</v>
+        <v>-0.7298</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5276</v>
+        <v>-0.3337</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4189</v>
+        <v>-0.3961</v>
       </c>
       <c r="P21" t="n">
         <v>0.3964</v>
@@ -2092,22 +2092,22 @@
         <v>0.3964</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.174</v>
+        <v>0.1854</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5616</v>
+        <v>0.056</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6124000000000001</v>
+        <v>0.1294</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2163</v>
+        <v>-0.8701</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3873</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4976</v>
+        <v>-1.0516</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8835</v>
+        <v>1.1892</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3811</v>
+        <v>-2.2407</v>
       </c>
       <c r="G22" t="n">
         <v>0.5396</v>
@@ -2170,13 +2170,13 @@
         <v>0.1982</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7617</v>
+        <v>-0.3157</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3744</v>
+        <v>-0.0688</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3873</v>
+        <v>-0.2469</v>
       </c>
       <c r="V22" t="n">
         <v>-1.4737</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.739</v>
+        <v>-2.6881</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5674</v>
+        <v>-0.0581</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1716</v>
+        <v>-2.63</v>
       </c>
       <c r="G23" t="n">
         <v>0.8346</v>
@@ -2248,13 +2248,13 @@
         <v>0.9911</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4858</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2568</v>
+        <v>0.2525</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7426</v>
+        <v>0.2842</v>
       </c>
       <c r="V23" t="n">
         <v>-2.0772</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8963</v>
+        <v>-2.8402</v>
       </c>
       <c r="E24" t="n">
         <v>-0.993</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9033</v>
+        <v>-1.8472</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4015</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2966</v>
+        <v>-0.2405</v>
       </c>
       <c r="T24" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2342</v>
+        <v>-0.1781</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2071</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.7378</v>
+        <v>-6.3255</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5346</v>
+        <v>-3.1459</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.2032</v>
+        <v>-3.1797</v>
       </c>
       <c r="G25" t="n">
         <v>-2.3526</v>
@@ -2404,13 +2404,13 @@
         <v>0.9911</v>
       </c>
       <c r="S25" t="n">
-        <v>1.9074</v>
+        <v>1.3196</v>
       </c>
       <c r="T25" t="n">
-        <v>1.5934</v>
+        <v>0.9822</v>
       </c>
       <c r="U25" t="n">
-        <v>0.314</v>
+        <v>0.3375</v>
       </c>
       <c r="V25" t="n">
         <v>-0.337</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.5866</v>
+        <v>-8.801299999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.3895</v>
+        <v>-6.2689</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.1971</v>
+        <v>-2.5324</v>
       </c>
       <c r="G26" t="n">
         <v>-3.3616</v>
@@ -2482,13 +2482,13 @@
         <v>1.3876</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.3993</v>
+        <v>-0.614</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.3727</v>
+        <v>-0.2522</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.0266</v>
+        <v>-0.3618</v>
       </c>
       <c r="V26" t="n">
         <v>-0.2666</v>
@@ -2515,22 +2515,22 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-20.7423</v>
+        <v>-19.3842</v>
       </c>
       <c r="E27" t="n">
         <v>-0.2606000000000011</v>
       </c>
       <c r="F27" t="n">
-        <v>-20.4818</v>
+        <v>-19.1236</v>
       </c>
       <c r="G27" t="n">
-        <v>-5.620299999999999</v>
+        <v>-5.6203</v>
       </c>
       <c r="H27" t="n">
         <v>-0.3295999999999997</v>
       </c>
       <c r="I27" t="n">
-        <v>-5.2903</v>
+        <v>-5.290299999999999</v>
       </c>
       <c r="J27" t="n">
         <v>8.120899999999999</v>
@@ -2539,7 +2539,7 @@
         <v>8.942600000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.8216000000000001</v>
+        <v>-0.8216</v>
       </c>
       <c r="M27" t="n">
         <v>-13.7412</v>
@@ -2557,16 +2557,16 @@
         <v>-19.8222</v>
       </c>
       <c r="R27" t="n">
-        <v>6.9376</v>
+        <v>6.937600000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>0.5136999999999996</v>
+        <v>1.8719</v>
       </c>
       <c r="T27" t="n">
-        <v>2.332200000000001</v>
+        <v>2.3321</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.8186</v>
+        <v>-0.4602000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>-2.7512</v>
